--- a/homeworks/2/homework2_branch_correlating_history_of_1.xlsx
+++ b/homeworks/2/homework2_branch_correlating_history_of_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\github\cs1541\CS1541_Source\homeworks\2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\github\cs2410\CS2410_Spring2026\homeworks\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C42F3A-965C-4DB9-B130-466F9ADB4E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A74D8A-823F-40FB-83DF-4400131F702B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1665" yWindow="4410" windowWidth="27135" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t>Actual</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>n</t>
+  </si>
+  <si>
+    <t>NT</t>
   </si>
 </sst>
 </file>
@@ -419,28 +422,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
